--- a/artfynd/A 42012-2025 artfynd.xlsx
+++ b/artfynd/A 42012-2025 artfynd.xlsx
@@ -941,7 +941,7 @@
         <v>135326907</v>
       </c>
       <c r="B4" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
